--- a/quizzes/sculpture-14e-niveau1.xlsx
+++ b/quizzes/sculpture-14e-niveau1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56A79474-402E-459C-A272-892608EEAF96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260AF55A-A206-4301-8178-5272739F4F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -358,9 +358,6 @@
     <t>Tabernacle du Camposanto</t>
   </si>
   <si>
-    <t>https://commons.wikimedia.org/wiki/Category:Jean_P%C3%A9pin_de_Huy#/media/File:Gisant_Robert_II_Artois_Basilique_St_Denis_St_Denis_Seine_St_Denis_1.jpg</t>
-  </si>
-  <si>
     <t>Jean Pépin de Huy</t>
   </si>
   <si>
@@ -404,6 +401,9 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8e/Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_sibilla_01.JPG/1280px-Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_sibilla_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d1/Gisant_Robert_II_Artois_Basilique_St_Denis_St_Denis_Seine_St_Denis_1.jpg/1280px-Gisant_Robert_II_Artois_Basilique_St_Denis_St_Denis_Seine_St_Denis_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -469,11 +469,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -812,16 +811,16 @@
       <c r="A2" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="3">
         <v>1336</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>105</v>
       </c>
     </row>
@@ -869,7 +868,7 @@
       <c r="C5" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>84</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -1082,7 +1081,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>13</v>
@@ -1099,7 +1098,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>13</v>
@@ -1111,12 +1110,12 @@
         <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>13</v>
@@ -1128,7 +1127,7 @@
         <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1167,19 +1166,19 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1203,16 +1202,16 @@
       <c r="A25" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="1" t="s">
         <v>110</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="1" t="s">
         <v>111</v>
       </c>
     </row>
@@ -1235,36 +1234,36 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="E27" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1347,12 +1346,12 @@
     <hyperlink ref="A29" r:id="rId22" xr:uid="{51F9677D-00A0-47B3-8171-ADB51AD7FB26}"/>
     <hyperlink ref="A2" r:id="rId23" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/eb/Agnolo_di_ventura%2C_portale_della_cappella_petroni%2C_1336%2C_02_madonna_col_bambino_tra_s._francesco_e_il_beato_pietro_da_siena.jpg/1280px-Agnolo_di_ventura%2C_portale_della_cappella_petroni%2C_1336%2C_02_madonna_col_bambino_tra_s._francesco_e_il_beato_pietro_da_siena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{121BBF53-75F1-470E-B536-3B0A3FDD2006}"/>
     <hyperlink ref="A25" r:id="rId24" xr:uid="{3B700743-FFC6-4A14-B16C-54ECEFD28E86}"/>
-    <hyperlink ref="A23" r:id="rId25" location="/media/File:Gisant_Robert_II_Artois_Basilique_St_Denis_St_Denis_Seine_St_Denis_1.jpg" xr:uid="{32C25DFF-A24E-43BB-8D3D-50E6D9BD54AF}"/>
-    <hyperlink ref="A27" r:id="rId26" xr:uid="{10039D00-6018-4518-8693-67CDB24D34C4}"/>
-    <hyperlink ref="A28" r:id="rId27" xr:uid="{4E253675-B8B6-4EE9-9C80-2A4F53A3A38F}"/>
-    <hyperlink ref="A19" r:id="rId28" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/37/Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_virt%C3%B9_teologali_%28fede%2C_speranza_e_carit%C3%A0%29_sulle_arti_del_trivio%2C_quadrivio_e_filosofia_03.JPG/1280px-Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_virt%C3%B9_teologali_%28fede%2C_speranza_e_carit%C3%A0%29_sulle_arti_del_trivio%2C_quadrivio_e_filosofia_03.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{32E6BCED-D9B1-4B50-A8F0-89C4AD745FAD}"/>
-    <hyperlink ref="A20" r:id="rId29" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f1/Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_stiloforo_02.JPG/1280px-Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_stiloforo_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8908619F-AE27-4D7B-93EC-AE55392CC5B5}"/>
-    <hyperlink ref="A18" r:id="rId30" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8e/Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_sibilla_01.JPG/1280px-Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_sibilla_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{90B93897-B7E5-4797-A94E-CFB9979833B4}"/>
+    <hyperlink ref="A27" r:id="rId25" xr:uid="{10039D00-6018-4518-8693-67CDB24D34C4}"/>
+    <hyperlink ref="A28" r:id="rId26" xr:uid="{4E253675-B8B6-4EE9-9C80-2A4F53A3A38F}"/>
+    <hyperlink ref="A19" r:id="rId27" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/37/Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_virt%C3%B9_teologali_%28fede%2C_speranza_e_carit%C3%A0%29_sulle_arti_del_trivio%2C_quadrivio_e_filosofia_03.JPG/1280px-Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_virt%C3%B9_teologali_%28fede%2C_speranza_e_carit%C3%A0%29_sulle_arti_del_trivio%2C_quadrivio_e_filosofia_03.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{32E6BCED-D9B1-4B50-A8F0-89C4AD745FAD}"/>
+    <hyperlink ref="A20" r:id="rId28" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f1/Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_stiloforo_02.JPG/1280px-Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_stiloforo_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8908619F-AE27-4D7B-93EC-AE55392CC5B5}"/>
+    <hyperlink ref="A18" r:id="rId29" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8e/Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_sibilla_01.JPG/1280px-Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_sibilla_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{90B93897-B7E5-4797-A94E-CFB9979833B4}"/>
+    <hyperlink ref="A23" r:id="rId30" display="https://upload.wikimedia.org/wikipedia/commons/thumb/d/d1/Gisant_Robert_II_Artois_Basilique_St_Denis_St_Denis_Seine_St_Denis_1.jpg/1280px-Gisant_Robert_II_Artois_Basilique_St_Denis_St_Denis_Seine_St_Denis_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8EA5FA40-AFF0-442B-A913-A15BFE2BC455}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId31"/>

--- a/quizzes/sculpture-14e-niveau1.xlsx
+++ b/quizzes/sculpture-14e-niveau1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260AF55A-A206-4301-8178-5272739F4F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A4C460-79BE-4FD6-B5E4-F66FC4FC0148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -337,9 +337,6 @@
     <t>Agnolo di Ventura</t>
   </si>
   <si>
-    <t>Portail de la chapelle Ptroni</t>
-  </si>
-  <si>
     <t>Basilique San Francesco, Sienne</t>
   </si>
   <si>
@@ -404,6 +401,9 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d1/Gisant_Robert_II_Artois_Basilique_St_Denis_St_Denis_Seine_St_Denis_1.jpg/1280px-Gisant_Robert_II_Artois_Basilique_St_Denis_St_Denis_Seine_St_Denis_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Portail de la chapelle Petroni</t>
   </si>
 </sst>
 </file>
@@ -818,10 +818,10 @@
         <v>1336</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1081,7 +1081,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>13</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>13</v>
@@ -1110,12 +1110,12 @@
         <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>13</v>
@@ -1127,7 +1127,7 @@
         <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1166,19 +1166,19 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1200,19 +1200,19 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C25" s="1" t="s">
+      <c r="E25" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1234,36 +1234,36 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C27" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
